--- a/dis_dye_list.xlsx
+++ b/dis_dye_list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3F11\Desktop\암호화파일 만들기\real data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3F11\Desktop\XML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC6E0F0D-A1B7-4BD7-976F-4A25E10F5956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B366ECC8-4124-4332-9933-9F551ABDDF6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="165" yWindow="210" windowWidth="15960" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="341">
   <si>
     <t>Suncron Yellow Brown S-FW_Interlock</t>
   </si>
@@ -919,18 +919,12 @@
     <t>Suncron Black S-N 300% ECO</t>
   </si>
   <si>
-    <t>Suncron Black S-PN ECO</t>
-  </si>
-  <si>
     <t>Suncron Black S-SFO 300% ECO</t>
   </si>
   <si>
     <t>Suncron Black S-SH ECO</t>
   </si>
   <si>
-    <t>Suncron Black S-TRF ECO</t>
-  </si>
-  <si>
     <t>Suncron Black T-FW ECO</t>
   </si>
   <si>
@@ -1004,27 +998,6 @@
   </si>
   <si>
     <t>Suncron Black CP-D</t>
-  </si>
-  <si>
-    <t>Daenong</t>
-  </si>
-  <si>
-    <t>Alrowad</t>
-  </si>
-  <si>
-    <t>UFS</t>
-  </si>
-  <si>
-    <t>P.P. COLOUR</t>
-  </si>
-  <si>
-    <t>Texco Tech</t>
-  </si>
-  <si>
-    <t>Quimtia</t>
-  </si>
-  <si>
-    <t>일신방직</t>
   </si>
   <si>
     <t>Suncron Navy Blue S-2GL 220% ECO</t>
@@ -1032,6 +1005,58 @@
   </si>
   <si>
     <t>Suncron Power Black CP-D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncron S-FW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncron T-FW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncron APEX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncron CP-D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncron SP-SE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncron RD-E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncron S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncron Black S-TRF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncron Black S-PN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncron E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncron Brilliant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncron SE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncron Fluorescent</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1381,15 +1406,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K123"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="48.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>1</v>
       </c>
@@ -1402,8 +1428,11 @@
       <c r="D1" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1416,11 +1445,11 @@
       <c r="D2" t="s">
         <v>239</v>
       </c>
-      <c r="F2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1433,11 +1462,11 @@
       <c r="D3" t="s">
         <v>240</v>
       </c>
-      <c r="G3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1450,11 +1479,11 @@
       <c r="D4" t="s">
         <v>241</v>
       </c>
-      <c r="J4" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1467,8 +1496,11 @@
       <c r="D5" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E5" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1481,8 +1513,11 @@
       <c r="D6" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3</v>
       </c>
@@ -1493,13 +1528,13 @@
         <v>203</v>
       </c>
       <c r="D7" t="s">
-        <v>311</v>
-      </c>
-      <c r="H7" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>309</v>
+      </c>
+      <c r="E7" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3</v>
       </c>
@@ -1512,14 +1547,11 @@
       <c r="D8" t="s">
         <v>244</v>
       </c>
-      <c r="F8" t="s">
-        <v>329</v>
-      </c>
-      <c r="I8" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>3</v>
       </c>
@@ -1532,17 +1564,11 @@
       <c r="D9" t="s">
         <v>245</v>
       </c>
-      <c r="F9" t="s">
-        <v>329</v>
-      </c>
-      <c r="G9" t="s">
-        <v>330</v>
-      </c>
-      <c r="H9" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3</v>
       </c>
@@ -1555,14 +1581,11 @@
       <c r="D10" t="s">
         <v>246</v>
       </c>
-      <c r="G10" t="s">
-        <v>330</v>
-      </c>
-      <c r="J10" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>5</v>
       </c>
@@ -1575,11 +1598,11 @@
       <c r="D11" t="s">
         <v>247</v>
       </c>
-      <c r="G11" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E11" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>6</v>
       </c>
@@ -1592,20 +1615,11 @@
       <c r="D12" t="s">
         <v>248</v>
       </c>
-      <c r="F12" t="s">
-        <v>329</v>
-      </c>
-      <c r="G12" t="s">
-        <v>330</v>
-      </c>
-      <c r="H12" t="s">
-        <v>331</v>
-      </c>
-      <c r="I12" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E12" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>6</v>
       </c>
@@ -1618,8 +1632,11 @@
       <c r="D13" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E13" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>6</v>
       </c>
@@ -1632,8 +1649,11 @@
       <c r="D14" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E14" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>6</v>
       </c>
@@ -1646,11 +1666,11 @@
       <c r="D15" t="s">
         <v>251</v>
       </c>
-      <c r="J15" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E15" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>6</v>
       </c>
@@ -1663,11 +1683,11 @@
       <c r="D16" t="s">
         <v>129</v>
       </c>
-      <c r="H16" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E16" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1</v>
       </c>
@@ -1680,11 +1700,11 @@
       <c r="D17" t="s">
         <v>252</v>
       </c>
-      <c r="F17" t="s">
+      <c r="E17" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1</v>
       </c>
@@ -1697,11 +1717,11 @@
       <c r="D18" t="s">
         <v>253</v>
       </c>
-      <c r="I18" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -1714,11 +1734,11 @@
       <c r="D19" t="s">
         <v>254</v>
       </c>
-      <c r="F19" t="s">
+      <c r="E19" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>3</v>
       </c>
@@ -1732,22 +1752,10 @@
         <v>255</v>
       </c>
       <c r="E20" t="s">
-        <v>328</v>
-      </c>
-      <c r="F20" t="s">
         <v>329</v>
       </c>
-      <c r="G20" t="s">
-        <v>330</v>
-      </c>
-      <c r="I20" t="s">
-        <v>332</v>
-      </c>
-      <c r="J20" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>3</v>
       </c>
@@ -1760,11 +1768,11 @@
       <c r="D21" t="s">
         <v>256</v>
       </c>
-      <c r="J21" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E21" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>3</v>
       </c>
@@ -1777,8 +1785,11 @@
       <c r="D22" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E22" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>3</v>
       </c>
@@ -1791,8 +1802,11 @@
       <c r="D23" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E23" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -1805,14 +1819,11 @@
       <c r="D24" t="s">
         <v>137</v>
       </c>
-      <c r="I24" t="s">
-        <v>332</v>
-      </c>
-      <c r="J24" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E24" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>5</v>
       </c>
@@ -1825,20 +1836,11 @@
       <c r="D25" t="s">
         <v>258</v>
       </c>
-      <c r="G25" t="s">
-        <v>330</v>
-      </c>
-      <c r="H25" t="s">
-        <v>331</v>
-      </c>
-      <c r="I25" t="s">
-        <v>332</v>
-      </c>
-      <c r="J25" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E25" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>6</v>
       </c>
@@ -1851,8 +1853,11 @@
       <c r="D26" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E26" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>6</v>
       </c>
@@ -1865,11 +1870,11 @@
       <c r="D27" t="s">
         <v>232</v>
       </c>
-      <c r="G27" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E27" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>6</v>
       </c>
@@ -1882,14 +1887,11 @@
       <c r="D28" t="s">
         <v>260</v>
       </c>
-      <c r="F28" t="s">
+      <c r="E28" t="s">
         <v>329</v>
       </c>
-      <c r="G28" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>6</v>
       </c>
@@ -1903,13 +1905,10 @@
         <v>261</v>
       </c>
       <c r="E29" t="s">
-        <v>328</v>
-      </c>
-      <c r="G29" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1</v>
       </c>
@@ -1922,17 +1921,11 @@
       <c r="D30" t="s">
         <v>142</v>
       </c>
-      <c r="F30" t="s">
-        <v>329</v>
-      </c>
-      <c r="G30" t="s">
+      <c r="E30" t="s">
         <v>330</v>
       </c>
-      <c r="I30" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1</v>
       </c>
@@ -1945,23 +1938,11 @@
       <c r="D31" t="s">
         <v>143</v>
       </c>
-      <c r="F31" t="s">
-        <v>329</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="E31" t="s">
         <v>330</v>
       </c>
-      <c r="H31" t="s">
-        <v>331</v>
-      </c>
-      <c r="I31" t="s">
-        <v>332</v>
-      </c>
-      <c r="J31" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -1974,20 +1955,11 @@
       <c r="D32" t="s">
         <v>144</v>
       </c>
-      <c r="F32" t="s">
-        <v>329</v>
-      </c>
-      <c r="G32" t="s">
+      <c r="E32" t="s">
         <v>330</v>
       </c>
-      <c r="H32" t="s">
-        <v>331</v>
-      </c>
-      <c r="I32" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>5</v>
       </c>
@@ -2000,20 +1972,11 @@
       <c r="D33" t="s">
         <v>145</v>
       </c>
-      <c r="F33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G33" t="s">
+      <c r="E33" t="s">
         <v>330</v>
       </c>
-      <c r="H33" t="s">
-        <v>331</v>
-      </c>
-      <c r="I33" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>6</v>
       </c>
@@ -2026,8 +1989,11 @@
       <c r="D34" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E34" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>6</v>
       </c>
@@ -2040,23 +2006,11 @@
       <c r="D35" t="s">
         <v>146</v>
       </c>
-      <c r="F35" t="s">
-        <v>329</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="E35" t="s">
         <v>330</v>
       </c>
-      <c r="H35" t="s">
-        <v>331</v>
-      </c>
-      <c r="I35" t="s">
-        <v>332</v>
-      </c>
-      <c r="J35" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>8</v>
       </c>
@@ -2069,23 +2023,11 @@
       <c r="D36" t="s">
         <v>147</v>
       </c>
-      <c r="F36" t="s">
-        <v>329</v>
-      </c>
-      <c r="G36" t="s">
+      <c r="E36" t="s">
         <v>330</v>
       </c>
-      <c r="H36" t="s">
-        <v>331</v>
-      </c>
-      <c r="I36" t="s">
-        <v>332</v>
-      </c>
-      <c r="J36" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1</v>
       </c>
@@ -2098,17 +2040,11 @@
       <c r="D37" t="s">
         <v>262</v>
       </c>
-      <c r="F37" t="s">
-        <v>329</v>
-      </c>
-      <c r="G37" t="s">
-        <v>330</v>
-      </c>
-      <c r="H37" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E37" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1</v>
       </c>
@@ -2121,23 +2057,11 @@
       <c r="D38" t="s">
         <v>263</v>
       </c>
-      <c r="F38" t="s">
-        <v>329</v>
-      </c>
-      <c r="G38" t="s">
-        <v>330</v>
-      </c>
-      <c r="H38" t="s">
-        <v>331</v>
-      </c>
-      <c r="I38" t="s">
-        <v>332</v>
-      </c>
-      <c r="J38" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E38" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1</v>
       </c>
@@ -2147,11 +2071,11 @@
       <c r="D39" t="s">
         <v>264</v>
       </c>
-      <c r="F39" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E39" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1</v>
       </c>
@@ -2165,22 +2089,10 @@
         <v>265</v>
       </c>
       <c r="E40" t="s">
-        <v>328</v>
-      </c>
-      <c r="F40" t="s">
-        <v>329</v>
-      </c>
-      <c r="G40" t="s">
-        <v>330</v>
-      </c>
-      <c r="H40" t="s">
-        <v>331</v>
-      </c>
-      <c r="J40" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1</v>
       </c>
@@ -2193,8 +2105,11 @@
       <c r="D41" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E41" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>2</v>
       </c>
@@ -2207,8 +2122,11 @@
       <c r="D42" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E42" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -2221,14 +2139,11 @@
       <c r="D43" t="s">
         <v>268</v>
       </c>
-      <c r="H43" t="s">
-        <v>331</v>
-      </c>
-      <c r="K43" t="s">
+      <c r="E43" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>3</v>
       </c>
@@ -2241,11 +2156,11 @@
       <c r="D44" t="s">
         <v>269</v>
       </c>
-      <c r="K44" t="s">
+      <c r="E44" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>3</v>
       </c>
@@ -2258,8 +2173,11 @@
       <c r="D45" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E45" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>3</v>
       </c>
@@ -2272,11 +2190,11 @@
       <c r="D46" t="s">
         <v>271</v>
       </c>
-      <c r="F46" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E46" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>3</v>
       </c>
@@ -2289,8 +2207,11 @@
       <c r="D47" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E47" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>3</v>
       </c>
@@ -2303,8 +2224,11 @@
       <c r="D48" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E48" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>3</v>
       </c>
@@ -2317,11 +2241,11 @@
       <c r="D49" t="s">
         <v>158</v>
       </c>
-      <c r="F49" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E49" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>5</v>
       </c>
@@ -2334,14 +2258,11 @@
       <c r="D50" t="s">
         <v>273</v>
       </c>
-      <c r="F50" t="s">
-        <v>329</v>
-      </c>
-      <c r="I50" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E50" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>5</v>
       </c>
@@ -2354,17 +2275,11 @@
       <c r="D51" t="s">
         <v>274</v>
       </c>
-      <c r="F51" t="s">
-        <v>329</v>
-      </c>
-      <c r="H51" t="s">
-        <v>331</v>
-      </c>
-      <c r="J51" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E51" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>5</v>
       </c>
@@ -2377,8 +2292,11 @@
       <c r="D52" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E52" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>5</v>
       </c>
@@ -2391,8 +2309,11 @@
       <c r="D53" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E53" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>6</v>
       </c>
@@ -2405,14 +2326,11 @@
       <c r="D54" t="s">
         <v>277</v>
       </c>
-      <c r="G54" t="s">
-        <v>330</v>
-      </c>
-      <c r="H54" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E54" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>6</v>
       </c>
@@ -2426,22 +2344,10 @@
         <v>278</v>
       </c>
       <c r="E55" t="s">
-        <v>328</v>
-      </c>
-      <c r="F55" t="s">
-        <v>329</v>
-      </c>
-      <c r="H55" t="s">
-        <v>331</v>
-      </c>
-      <c r="I55" t="s">
-        <v>332</v>
-      </c>
-      <c r="J55" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>6</v>
       </c>
@@ -2454,28 +2360,22 @@
       <c r="D56" t="s">
         <v>279</v>
       </c>
-      <c r="F56" t="s">
-        <v>329</v>
-      </c>
-      <c r="H56" t="s">
-        <v>331</v>
-      </c>
-      <c r="I56" t="s">
-        <v>332</v>
-      </c>
-      <c r="K56" t="s">
+      <c r="E56" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C57" t="s">
         <v>229</v>
       </c>
       <c r="D57" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+        <v>326</v>
+      </c>
+      <c r="E57" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>7</v>
       </c>
@@ -2488,8 +2388,11 @@
       <c r="D58" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E58" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -2502,8 +2405,11 @@
       <c r="D59" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E59" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1</v>
       </c>
@@ -2516,14 +2422,11 @@
       <c r="D60" t="s">
         <v>282</v>
       </c>
-      <c r="H60" t="s">
-        <v>331</v>
-      </c>
-      <c r="I60" t="s">
+      <c r="E60" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>3</v>
       </c>
@@ -2536,14 +2439,11 @@
       <c r="D61" t="s">
         <v>283</v>
       </c>
-      <c r="H61" t="s">
-        <v>331</v>
-      </c>
-      <c r="I61" t="s">
+      <c r="E61" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -2556,14 +2456,11 @@
       <c r="D62" t="s">
         <v>284</v>
       </c>
-      <c r="H62" t="s">
-        <v>331</v>
-      </c>
-      <c r="I62" t="s">
+      <c r="E62" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1</v>
       </c>
@@ -2576,14 +2473,11 @@
       <c r="D63" t="s">
         <v>285</v>
       </c>
-      <c r="F63" t="s">
-        <v>329</v>
-      </c>
-      <c r="I63" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E63" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1</v>
       </c>
@@ -2596,17 +2490,11 @@
       <c r="D64" t="s">
         <v>286</v>
       </c>
-      <c r="F64" t="s">
-        <v>329</v>
-      </c>
-      <c r="H64" t="s">
-        <v>331</v>
-      </c>
-      <c r="J64" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E64" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>3</v>
       </c>
@@ -2619,14 +2507,11 @@
       <c r="D65" t="s">
         <v>287</v>
       </c>
-      <c r="I65" t="s">
-        <v>332</v>
-      </c>
-      <c r="J65" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E65" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>3</v>
       </c>
@@ -2639,14 +2524,11 @@
       <c r="D66" t="s">
         <v>288</v>
       </c>
-      <c r="H66" t="s">
-        <v>331</v>
-      </c>
-      <c r="I66" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E66" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>3</v>
       </c>
@@ -2659,11 +2541,11 @@
       <c r="D67" t="s">
         <v>289</v>
       </c>
-      <c r="J67" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E67" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>5</v>
       </c>
@@ -2676,8 +2558,11 @@
       <c r="D68" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E68" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>5</v>
       </c>
@@ -2690,14 +2575,11 @@
       <c r="D69" t="s">
         <v>291</v>
       </c>
-      <c r="F69" t="s">
-        <v>329</v>
-      </c>
-      <c r="H69" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E69" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>5</v>
       </c>
@@ -2710,11 +2592,11 @@
       <c r="D70" t="s">
         <v>292</v>
       </c>
-      <c r="G70" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E70" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>6</v>
       </c>
@@ -2728,16 +2610,10 @@
         <v>293</v>
       </c>
       <c r="E71" t="s">
-        <v>328</v>
-      </c>
-      <c r="F71" t="s">
-        <v>329</v>
-      </c>
-      <c r="J71" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>7</v>
       </c>
@@ -2750,14 +2626,11 @@
       <c r="D72" t="s">
         <v>294</v>
       </c>
-      <c r="F72" t="s">
-        <v>329</v>
-      </c>
-      <c r="J72" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E72" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>8</v>
       </c>
@@ -2770,8 +2643,11 @@
       <c r="D73" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E73" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>8</v>
       </c>
@@ -2784,8 +2660,11 @@
       <c r="D74" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E74" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>8</v>
       </c>
@@ -2799,7 +2678,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>8</v>
       </c>
@@ -2812,11 +2691,11 @@
       <c r="D76" t="s">
         <v>297</v>
       </c>
-      <c r="H76" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E76" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>8</v>
       </c>
@@ -2829,8 +2708,11 @@
       <c r="D77" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E77" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>8</v>
       </c>
@@ -2843,17 +2725,11 @@
       <c r="D78" t="s">
         <v>182</v>
       </c>
-      <c r="F78" t="s">
-        <v>329</v>
-      </c>
-      <c r="G78" t="s">
-        <v>330</v>
-      </c>
-      <c r="J78" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E78" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>8</v>
       </c>
@@ -2864,10 +2740,13 @@
         <v>187</v>
       </c>
       <c r="D79" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+        <v>336</v>
+      </c>
+      <c r="E79" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>8</v>
       </c>
@@ -2878,22 +2757,13 @@
         <v>188</v>
       </c>
       <c r="D80" t="s">
-        <v>300</v>
-      </c>
-      <c r="F80" t="s">
-        <v>329</v>
-      </c>
-      <c r="G80" t="s">
-        <v>330</v>
-      </c>
-      <c r="I80" t="s">
-        <v>332</v>
-      </c>
-      <c r="J80" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+        <v>299</v>
+      </c>
+      <c r="E80" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>8</v>
       </c>
@@ -2904,10 +2774,13 @@
         <v>189</v>
       </c>
       <c r="D81" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+      <c r="E81" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>8</v>
       </c>
@@ -2918,10 +2791,13 @@
         <v>190</v>
       </c>
       <c r="D82" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+        <v>335</v>
+      </c>
+      <c r="E82" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>8</v>
       </c>
@@ -2934,14 +2810,11 @@
       <c r="D83" t="s">
         <v>191</v>
       </c>
-      <c r="G83" t="s">
-        <v>330</v>
-      </c>
-      <c r="H83" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E83" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>8</v>
       </c>
@@ -2954,8 +2827,11 @@
       <c r="D84" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E84" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>8</v>
       </c>
@@ -2966,22 +2842,13 @@
         <v>193</v>
       </c>
       <c r="D85" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E85" t="s">
-        <v>328</v>
-      </c>
-      <c r="G85" t="s">
-        <v>330</v>
-      </c>
-      <c r="I85" t="s">
-        <v>332</v>
-      </c>
-      <c r="J85" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>8</v>
       </c>
@@ -2992,10 +2859,13 @@
         <v>194</v>
       </c>
       <c r="D86" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+        <v>302</v>
+      </c>
+      <c r="E86" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>8</v>
       </c>
@@ -3006,10 +2876,13 @@
         <v>195</v>
       </c>
       <c r="D87" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+        <v>303</v>
+      </c>
+      <c r="E87" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>8</v>
       </c>
@@ -3020,13 +2893,13 @@
         <v>196</v>
       </c>
       <c r="D88" t="s">
-        <v>306</v>
-      </c>
-      <c r="I88" t="s">
+        <v>304</v>
+      </c>
+      <c r="E88" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>8</v>
       </c>
@@ -3037,16 +2910,13 @@
         <v>198</v>
       </c>
       <c r="D89" t="s">
-        <v>307</v>
-      </c>
-      <c r="F89" t="s">
-        <v>329</v>
-      </c>
-      <c r="G89" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+      <c r="E89" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>1</v>
       </c>
@@ -3057,19 +2927,13 @@
         <v>199</v>
       </c>
       <c r="D90" t="s">
-        <v>308</v>
-      </c>
-      <c r="F90" t="s">
-        <v>329</v>
-      </c>
-      <c r="I90" t="s">
-        <v>332</v>
-      </c>
-      <c r="K90" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+      <c r="E90" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>2</v>
       </c>
@@ -3082,11 +2946,11 @@
       <c r="D91" t="s">
         <v>85</v>
       </c>
-      <c r="H91" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E91" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>2</v>
       </c>
@@ -3099,14 +2963,11 @@
       <c r="D92" t="s">
         <v>200</v>
       </c>
-      <c r="F92" t="s">
-        <v>329</v>
-      </c>
-      <c r="K92" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E92" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>2</v>
       </c>
@@ -3117,16 +2978,13 @@
         <v>201</v>
       </c>
       <c r="D93" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E93" t="s">
-        <v>328</v>
-      </c>
-      <c r="F93" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>3</v>
       </c>
@@ -3137,13 +2995,13 @@
         <v>202</v>
       </c>
       <c r="D94" t="s">
-        <v>310</v>
-      </c>
-      <c r="G94" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+        <v>308</v>
+      </c>
+      <c r="E94" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>3</v>
       </c>
@@ -3154,10 +3012,10 @@
         <v>204</v>
       </c>
       <c r="D95" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>3</v>
       </c>
@@ -3165,10 +3023,13 @@
         <v>92</v>
       </c>
       <c r="D96" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+        <v>311</v>
+      </c>
+      <c r="E96" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>7</v>
       </c>
@@ -3176,10 +3037,13 @@
         <v>206</v>
       </c>
       <c r="D97" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+        <v>312</v>
+      </c>
+      <c r="E97" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>7</v>
       </c>
@@ -3192,8 +3056,11 @@
       <c r="D98" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E98" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>5</v>
       </c>
@@ -3204,13 +3071,13 @@
         <v>208</v>
       </c>
       <c r="D99" t="s">
-        <v>315</v>
-      </c>
-      <c r="F99" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+        <v>313</v>
+      </c>
+      <c r="E99" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>5</v>
       </c>
@@ -3221,16 +3088,13 @@
         <v>209</v>
       </c>
       <c r="D100" t="s">
-        <v>316</v>
-      </c>
-      <c r="G100" t="s">
-        <v>330</v>
-      </c>
-      <c r="I100" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+        <v>314</v>
+      </c>
+      <c r="E100" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>6</v>
       </c>
@@ -3241,16 +3105,13 @@
         <v>210</v>
       </c>
       <c r="D101" t="s">
-        <v>317</v>
-      </c>
-      <c r="F101" t="s">
-        <v>329</v>
-      </c>
-      <c r="J101" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+      <c r="E101" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>1</v>
       </c>
@@ -3261,16 +3122,13 @@
         <v>211</v>
       </c>
       <c r="D102" t="s">
-        <v>318</v>
-      </c>
-      <c r="F102" t="s">
-        <v>329</v>
-      </c>
-      <c r="I102" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+        <v>316</v>
+      </c>
+      <c r="E102" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>2</v>
       </c>
@@ -3278,16 +3136,13 @@
         <v>98</v>
       </c>
       <c r="D103" t="s">
-        <v>319</v>
-      </c>
-      <c r="F103" t="s">
-        <v>329</v>
-      </c>
-      <c r="I103" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+        <v>317</v>
+      </c>
+      <c r="E103" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>3</v>
       </c>
@@ -3298,19 +3153,13 @@
         <v>212</v>
       </c>
       <c r="D104" t="s">
-        <v>320</v>
-      </c>
-      <c r="F104" t="s">
-        <v>329</v>
-      </c>
-      <c r="H104" t="s">
-        <v>331</v>
-      </c>
-      <c r="I104" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+        <v>318</v>
+      </c>
+      <c r="E104" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>3</v>
       </c>
@@ -3321,16 +3170,13 @@
         <v>213</v>
       </c>
       <c r="D105" t="s">
-        <v>321</v>
-      </c>
-      <c r="G105" t="s">
-        <v>330</v>
-      </c>
-      <c r="I105" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+      <c r="E105" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>5</v>
       </c>
@@ -3341,10 +3187,13 @@
         <v>214</v>
       </c>
       <c r="D106" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+        <v>320</v>
+      </c>
+      <c r="E106" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>5</v>
       </c>
@@ -3355,19 +3204,13 @@
         <v>214</v>
       </c>
       <c r="D107" t="s">
-        <v>323</v>
-      </c>
-      <c r="F107" t="s">
-        <v>329</v>
-      </c>
-      <c r="G107" t="s">
-        <v>330</v>
-      </c>
-      <c r="H107" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+        <v>321</v>
+      </c>
+      <c r="E107" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>1</v>
       </c>
@@ -3378,22 +3221,13 @@
         <v>215</v>
       </c>
       <c r="D108" t="s">
-        <v>324</v>
-      </c>
-      <c r="F108" t="s">
-        <v>329</v>
-      </c>
-      <c r="G108" t="s">
-        <v>330</v>
-      </c>
-      <c r="H108" t="s">
-        <v>331</v>
-      </c>
-      <c r="I108" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+        <v>322</v>
+      </c>
+      <c r="E108" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>3</v>
       </c>
@@ -3404,22 +3238,13 @@
         <v>205</v>
       </c>
       <c r="D109" t="s">
-        <v>325</v>
-      </c>
-      <c r="F109" t="s">
-        <v>329</v>
-      </c>
-      <c r="G109" t="s">
-        <v>330</v>
-      </c>
-      <c r="H109" t="s">
-        <v>331</v>
-      </c>
-      <c r="I109" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+        <v>323</v>
+      </c>
+      <c r="E109" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>5</v>
       </c>
@@ -3430,22 +3255,13 @@
         <v>216</v>
       </c>
       <c r="D110" t="s">
-        <v>326</v>
-      </c>
-      <c r="F110" t="s">
-        <v>329</v>
-      </c>
-      <c r="G110" t="s">
-        <v>330</v>
-      </c>
-      <c r="H110" t="s">
-        <v>331</v>
-      </c>
-      <c r="I110" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+      <c r="E110" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>1</v>
       </c>
@@ -3458,8 +3274,11 @@
       <c r="D111" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E111" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>3</v>
       </c>
@@ -3472,8 +3291,11 @@
       <c r="D112" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E112" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>5</v>
       </c>
@@ -3486,8 +3308,11 @@
       <c r="D113" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E113" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>1</v>
       </c>
@@ -3500,8 +3325,11 @@
       <c r="D114" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E114" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>1</v>
       </c>
@@ -3514,8 +3342,11 @@
       <c r="D115" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E115" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>3</v>
       </c>
@@ -3528,8 +3359,11 @@
       <c r="D116" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E116" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>3</v>
       </c>
@@ -3542,8 +3376,11 @@
       <c r="D117" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E117" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>5</v>
       </c>
@@ -3556,8 +3393,11 @@
       <c r="D118" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E118" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>6</v>
       </c>
@@ -3570,8 +3410,11 @@
       <c r="D119" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E119" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>6</v>
       </c>
@@ -3584,8 +3427,11 @@
       <c r="D120" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E120" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>7</v>
       </c>
@@ -3598,8 +3444,11 @@
       <c r="D121" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E121" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>8</v>
       </c>
@@ -3610,10 +3459,13 @@
         <v>228</v>
       </c>
       <c r="D122" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+      <c r="E122" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>8</v>
       </c>
@@ -3624,7 +3476,10 @@
         <v>197</v>
       </c>
       <c r="D123" t="s">
-        <v>336</v>
+        <v>327</v>
+      </c>
+      <c r="E123" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>
